--- a/credentials_exports/Student_Credentials_Boys_and_Girls.xlsx
+++ b/credentials_exports/Student_Credentials_Boys_and_Girls.xlsx
@@ -17,7 +17,7 @@
     <t>SMART BUS ATTENDANCE - BOYS STUDENTS (21)</t>
   </si>
   <si>
-    <t>Bus: Bus No-09 | Route: College Bus No 09 | Total: 21 Students</t>
+    <t>Bus: BUS-09 | Route: College Bus No 09 | Total: 21 Students</t>
   </si>
   <si>
     <t>S.No</t>
@@ -68,7 +68,7 @@
     <t>student05@college.edu</t>
   </si>
   <si>
-    <t>Bus No-09</t>
+    <t>BUS-09</t>
   </si>
   <si>
     <t>23CS014</t>
@@ -410,7 +410,7 @@
     <t>SMART BUS ATTENDANCE - GIRLS STUDENTS (34)</t>
   </si>
   <si>
-    <t>Bus: Bus No-09 | Route: College Bus No 09 | Total: 34 Students</t>
+    <t>Bus: BUS-09 | Route: College Bus No 09 | Total: 34 Students</t>
   </si>
   <si>
     <t>23CS001</t>
